--- a/artfynd/A 56717-2024 artfynd.xlsx
+++ b/artfynd/A 56717-2024 artfynd.xlsx
@@ -675,50 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74112441</v>
+        <v>74112448</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gännorområdet, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719457.9885107339</v>
+        <v>719473</v>
       </c>
       <c r="R2" t="n">
-        <v>6391673.187300205</v>
+        <v>6391638</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,27 +745,18 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,19 +775,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74112442</v>
+        <v>74112441</v>
       </c>
       <c r="B3" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719331.1796611814</v>
+        <v>719458</v>
       </c>
       <c r="R3" t="n">
-        <v>6391671.143318163</v>
+        <v>6391673</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +843,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +872,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74112451</v>
+        <v>74112442</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +883,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719323.774483997</v>
+        <v>719331</v>
       </c>
       <c r="R4" t="n">
-        <v>6391658.933321494</v>
+        <v>6391671</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +940,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74112448</v>
+        <v>74112443</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,36 +980,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gännorområdet, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719472.8024182189</v>
+        <v>719382</v>
       </c>
       <c r="R5" t="n">
-        <v>6391638.027703854</v>
+        <v>6391693</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,28 +1037,17 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,15 +1066,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74112450</v>
+        <v>74112451</v>
       </c>
       <c r="B6" t="n">
-        <v>86195</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,21 +1077,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>239233</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1101,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719459.9454447204</v>
+        <v>719324</v>
       </c>
       <c r="R6" t="n">
-        <v>6391666.852319242</v>
+        <v>6391659</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,19 +1134,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56717-2024 artfynd.xlsx
+++ b/artfynd/A 56717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,8 +1185,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>